--- a/data/trans_camb/P43E-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P43E-Provincia-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-8,67</t>
+          <t>-9,42</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-8,67</t>
+          <t>-9,42</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 9,46</t>
+          <t>-8,4; 9,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -0,62</t>
+          <t>-18,1; -2,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 9,46</t>
+          <t>-8,4; 9,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -0,62</t>
+          <t>-18,1; -2,36</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-35,98%</t>
+          <t>-39,09%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-35,98%</t>
+          <t>-39,09%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,17; 50,21</t>
+          <t>-29,33; 49,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,56; -2,56</t>
+          <t>-60,3; -12,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,17; 50,21</t>
+          <t>-29,33; 49,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,56; -2,56</t>
+          <t>-60,3; -12,0</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,26</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,71; -0,48</t>
+          <t>-12,9; -1,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 11,53</t>
+          <t>-2,06; 11,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,71; -0,48</t>
+          <t>-12,9; -1,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 11,53</t>
+          <t>-2,06; 11,08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,29; -2,55</t>
+          <t>-50,75; -5,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 62,53</t>
+          <t>-8,35; 59,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,29; -2,55</t>
+          <t>-50,75; -5,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 62,53</t>
+          <t>-8,35; 59,79</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-8,11</t>
+          <t>-8,17</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-8,11</t>
+          <t>-8,17</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,11; -13,37</t>
+          <t>-27,72; -13,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,41; -0,42</t>
+          <t>-16,81; 0,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,11; -13,37</t>
+          <t>-27,72; -13,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,41; -0,42</t>
+          <t>-16,81; 0,23</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-31,81%</t>
+          <t>-32,06%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-31,81%</t>
+          <t>-32,06%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-90,3; -61,92</t>
+          <t>-90,38; -62,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,41; -1,06</t>
+          <t>-54,93; 2,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-90,3; -61,92</t>
+          <t>-90,38; -62,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,41; -1,06</t>
+          <t>-54,93; 2,07</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-13,01</t>
+          <t>-5,65</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-13,01</t>
+          <t>-5,65</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,9; -7,47</t>
+          <t>-21,84; -7,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,95; -4,25</t>
+          <t>-12,92; 1,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,9; -7,47</t>
+          <t>-21,84; -7,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,95; -4,25</t>
+          <t>-12,92; 1,15</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-49,74%</t>
+          <t>-21,6%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-49,74%</t>
+          <t>-21,6%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,32; -29,79</t>
+          <t>-72,81; -32,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,05; -17,67</t>
+          <t>-42,53; 6,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,32; -29,79</t>
+          <t>-72,81; -32,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,05; -17,67</t>
+          <t>-42,53; 6,31</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>4,13</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-19,59; -0,83</t>
+          <t>-19,14; -0,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 14,51</t>
+          <t>-4,81; 15,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,59; -0,83</t>
+          <t>-19,14; -0,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 14,51</t>
+          <t>-4,81; 15,41</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,38; 1,39</t>
+          <t>-73,36; 0,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 92,01</t>
+          <t>-18,52; 95,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-72,38; 1,39</t>
+          <t>-73,36; 0,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 92,01</t>
+          <t>-18,52; 95,33</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-0,8</t>
         </is>
       </c>
     </row>
@@ -1181,22 +1181,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 20,23</t>
+          <t>-5,99; 19,44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 8,9</t>
+          <t>-10,21; 8,35</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 20,23</t>
+          <t>-5,99; 19,44</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 8,9</t>
+          <t>-10,21; 8,35</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-4,59%</t>
+          <t>-4,17%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-4,59%</t>
+          <t>-4,17%</t>
         </is>
       </c>
     </row>
@@ -1237,22 +1237,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 136,74</t>
+          <t>-25,51; 135,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 69,27</t>
+          <t>-40,83; 58,46</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 136,74</t>
+          <t>-25,51; 135,21</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 69,27</t>
+          <t>-40,83; 58,46</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>18,38</t>
+          <t>17,38</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18,38</t>
+          <t>17,38</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 3,45</t>
+          <t>-7,93; 3,28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>12,16; 24,91</t>
+          <t>11,25; 23,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 3,45</t>
+          <t>-7,93; 3,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12,16; 24,91</t>
+          <t>11,25; 23,74</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,91; 17,04</t>
+          <t>-29,5; 15,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>44,38; 118,5</t>
+          <t>41,34; 116,23</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,91; 17,04</t>
+          <t>-29,5; 15,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44,38; 118,5</t>
+          <t>41,34; 116,23</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-7,77</t>
+          <t>-7,37</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-7,77</t>
+          <t>-7,37</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1413,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 1,02</t>
+          <t>-8,87; 1,78</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-13,23; -2,8</t>
+          <t>-12,31; -2,46</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 1,02</t>
+          <t>-8,87; 1,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-13,23; -2,8</t>
+          <t>-12,31; -2,46</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-36,0%</t>
+          <t>-34,14%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-36,0%</t>
+          <t>-34,14%</t>
         </is>
       </c>
     </row>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 5,43</t>
+          <t>-37,47; 10,18</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-54,77; -14,95</t>
+          <t>-51,89; -11,79</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 5,43</t>
+          <t>-37,47; 10,18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-54,77; -14,95</t>
+          <t>-51,89; -11,79</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>1,55</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -4,22</t>
+          <t>-9,14; -4,01</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,86</t>
+          <t>-1,2; 4,16</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -4,22</t>
+          <t>-9,14; -4,01</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,86</t>
+          <t>-1,2; 4,16</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-0,38%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-0,38%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -1585,22 +1585,22 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-37,29; -19,49</t>
+          <t>-37,77; -18,72</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 12,94</t>
+          <t>-4,99; 19,32</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-37,29; -19,49</t>
+          <t>-37,77; -18,72</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 12,94</t>
+          <t>-4,99; 19,32</t>
         </is>
       </c>
     </row>
